--- a/Errors.xlsx
+++ b/Errors.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{22C710D8-5ED0-4812-BCBF-356E8D029F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3975CB-BE00-4CFD-A1BD-9944EF6B09EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{30A902C1-FA37-4575-AF65-6E09AA660DA0}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{30A902C1-FA37-4575-AF65-6E09AA660DA0}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,8 +35,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="24">
   <si>
     <t>mt</t>
   </si>
@@ -96,16 +117,35 @@
     <t>routine_Ramos_N2O4_iter</t>
   </si>
   <si>
-    <t>nan</t>
+    <t>OLD</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>Means</t>
+  </si>
+  <si>
+    <t>delta</t>
+  </si>
+  <si>
+    <t>New with normalised DB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -132,10 +172,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -471,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{556AB3AE-072F-44CD-A5AF-40E7BF9562B8}">
-  <dimension ref="E4:N14"/>
+  <dimension ref="D4:R37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="6" max="6" width="15.5546875" customWidth="1"/>
@@ -485,7 +535,7 @@
     <col min="14" max="14" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="5:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="4:18" x14ac:dyDescent="0.3">
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
         <v>8</v>
@@ -514,8 +564,14 @@
       <c r="N4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="P4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D5" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="E5" t="s">
         <v>0</v>
       </c>
@@ -534,9 +590,7 @@
       <c r="J5" s="1">
         <v>6.03</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="K5" s="1"/>
       <c r="L5" s="1">
         <v>8.1300000000000008</v>
       </c>
@@ -546,8 +600,13 @@
       <c r="N5" s="1">
         <v>-3.27</v>
       </c>
-    </row>
-    <row r="6" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="P5" s="4" cm="1">
+        <f t="array" ref="P5">AVERAGEA(ABS(G5:N5))</f>
+        <v>3.8187500000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D6" s="2"/>
       <c r="E6" t="s">
         <v>1</v>
       </c>
@@ -566,9 +625,7 @@
       <c r="J6" s="1">
         <v>-0.4</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="K6" s="1"/>
       <c r="L6" s="1">
         <v>5.97</v>
       </c>
@@ -578,8 +635,13 @@
       <c r="N6" s="1">
         <v>-28.73</v>
       </c>
-    </row>
-    <row r="7" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="P6" s="4" cm="1">
+        <f t="array" ref="P6">AVERAGEA(ABS(G6:N6))</f>
+        <v>10.442499999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D7" s="2"/>
       <c r="E7" t="s">
         <v>2</v>
       </c>
@@ -598,9 +660,7 @@
       <c r="J7" s="1">
         <v>11.4</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="K7" s="1"/>
       <c r="L7" s="1">
         <v>13.6</v>
       </c>
@@ -610,8 +670,13 @@
       <c r="N7" s="1">
         <v>1.62</v>
       </c>
-    </row>
-    <row r="8" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="P7" s="4" cm="1">
+        <f t="array" ref="P7">AVERAGEA(ABS(G7:N7))</f>
+        <v>7.0075000000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D8" s="2"/>
       <c r="E8" t="s">
         <v>3</v>
       </c>
@@ -642,8 +707,13 @@
       <c r="N8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="P8" s="4" cm="1">
+        <f t="array" ref="P8">AVERAGEA(ABS(G8:N8))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D9" s="2"/>
       <c r="E9" t="s">
         <v>9</v>
       </c>
@@ -674,8 +744,13 @@
       <c r="N9" s="1">
         <v>-14.01</v>
       </c>
-    </row>
-    <row r="10" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="P9" s="4" cm="1">
+        <f t="array" ref="P9">AVERAGEA(ABS(G9:N9))</f>
+        <v>414.81125000000009</v>
+      </c>
+    </row>
+    <row r="10" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D10" s="2"/>
       <c r="E10" t="s">
         <v>4</v>
       </c>
@@ -694,9 +769,7 @@
       <c r="J10" s="1">
         <v>5.0199999999999996</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="K10" s="1"/>
       <c r="L10" s="1">
         <v>35.549999999999997</v>
       </c>
@@ -706,8 +779,13 @@
       <c r="N10" s="1">
         <v>-31.18</v>
       </c>
-    </row>
-    <row r="11" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="P10" s="4" cm="1">
+        <f t="array" ref="P10">AVERAGEA(ABS(G10:N10))</f>
+        <v>27.344999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D11" s="2"/>
       <c r="E11" t="s">
         <v>5</v>
       </c>
@@ -738,8 +816,13 @@
       <c r="N11" s="1">
         <v>355.27</v>
       </c>
-    </row>
-    <row r="12" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="P11" s="4" cm="1">
+        <f t="array" ref="P11">AVERAGEA(ABS(G11:N11))</f>
+        <v>6260.7825000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D12" s="2"/>
       <c r="E12" t="s">
         <v>6</v>
       </c>
@@ -770,8 +853,13 @@
       <c r="N12" s="1">
         <v>-6.64</v>
       </c>
-    </row>
-    <row r="13" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="P12" s="4" cm="1">
+        <f t="array" ref="P12">AVERAGEA(ABS(G12:N12))</f>
+        <v>329.44749999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D13" s="2"/>
       <c r="E13" t="s">
         <v>10</v>
       </c>
@@ -802,8 +890,13 @@
       <c r="N13" s="1">
         <v>-22.26</v>
       </c>
-    </row>
-    <row r="14" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="P13" s="4" cm="1">
+        <f t="array" ref="P13">AVERAGEA(ABS(G13:N13))</f>
+        <v>640.65</v>
+      </c>
+    </row>
+    <row r="14" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D14" s="2"/>
       <c r="E14" t="s">
         <v>7</v>
       </c>
@@ -834,44 +927,560 @@
       <c r="N14" s="1">
         <v>-38.71</v>
       </c>
+      <c r="P14" s="4" cm="1">
+        <f t="array" ref="P14">AVERAGEA(ABS(G14:N14))</f>
+        <v>517.34375</v>
+      </c>
+    </row>
+    <row r="15" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" t="s">
+        <v>14</v>
+      </c>
+      <c r="K15" t="s">
+        <v>15</v>
+      </c>
+      <c r="L15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N15" t="s">
+        <v>18</v>
+      </c>
+      <c r="R15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D16" s="2"/>
+      <c r="E16" t="s">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>-0.61399999999999999</v>
+      </c>
+      <c r="G16" s="1">
+        <v>-8.93</v>
+      </c>
+      <c r="H16" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="I16" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="J16" s="1">
+        <v>7.27</v>
+      </c>
+      <c r="K16" s="1">
+        <v>19.71</v>
+      </c>
+      <c r="L16" s="1">
+        <v>6.76</v>
+      </c>
+      <c r="M16" s="1">
+        <v>-5.0599999999999996</v>
+      </c>
+      <c r="N16" s="1">
+        <v>-11.17</v>
+      </c>
+      <c r="P16" s="4" cm="1">
+        <f t="array" ref="P16">AVERAGEA(ABS(G16:N16))</f>
+        <v>8.4625000000000004</v>
+      </c>
+      <c r="R16" s="3">
+        <f>P16-ABS(P5)</f>
+        <v>4.6437500000000007</v>
+      </c>
+    </row>
+    <row r="17" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D17" s="2"/>
+      <c r="E17" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1">
+        <v>-0.42499999999999999</v>
+      </c>
+      <c r="G17" s="1">
+        <v>-45.95</v>
+      </c>
+      <c r="H17" s="1">
+        <v>-5.39</v>
+      </c>
+      <c r="I17" s="1">
+        <v>-5.39</v>
+      </c>
+      <c r="J17" s="1">
+        <v>3.35</v>
+      </c>
+      <c r="K17" s="1">
+        <v>41.24</v>
+      </c>
+      <c r="L17" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="M17" s="1">
+        <v>-34.159999999999997</v>
+      </c>
+      <c r="N17" s="1">
+        <v>-52.77</v>
+      </c>
+      <c r="P17" s="4" cm="1">
+        <f t="array" ref="P17">AVERAGEA(ABS(G17:N17))</f>
+        <v>23.756250000000001</v>
+      </c>
+      <c r="R17" s="3">
+        <f>P17-ABS(P6)</f>
+        <v>13.313750000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D18" s="2"/>
+      <c r="E18" t="s">
+        <v>2</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1.32</v>
+      </c>
+      <c r="G18" s="1">
+        <v>-4.32</v>
+      </c>
+      <c r="H18" s="1">
+        <v>9.68</v>
+      </c>
+      <c r="I18" s="1">
+        <v>9.68</v>
+      </c>
+      <c r="J18" s="1">
+        <v>12.69</v>
+      </c>
+      <c r="K18" s="1">
+        <v>25.77</v>
+      </c>
+      <c r="L18" s="1">
+        <v>12.16</v>
+      </c>
+      <c r="M18" s="1">
+        <v>-0.25</v>
+      </c>
+      <c r="N18" s="1">
+        <v>-6.68</v>
+      </c>
+      <c r="P18" s="4" cm="1">
+        <f t="array" ref="P18">AVERAGEA(ABS(G18:N18))</f>
+        <v>10.153749999999999</v>
+      </c>
+      <c r="R18" s="3">
+        <f>P18-ABS(P7)</f>
+        <v>3.1462499999999984</v>
+      </c>
+    </row>
+    <row r="19" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D19" s="2"/>
+      <c r="E19" t="s">
+        <v>3</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1">
+        <v>0</v>
+      </c>
+      <c r="P19" s="4" cm="1">
+        <f t="array" ref="P19">AVERAGEA(ABS(G19:N19))</f>
+        <v>0</v>
+      </c>
+      <c r="R19" s="3">
+        <f>P19-ABS(P8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D20" s="2"/>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0.40200000000000002</v>
+      </c>
+      <c r="G20" s="1">
+        <v>-14.01</v>
+      </c>
+      <c r="H20" s="1">
+        <v>-14.01</v>
+      </c>
+      <c r="I20" s="1">
+        <v>-14.01</v>
+      </c>
+      <c r="J20" s="1">
+        <v>17.55</v>
+      </c>
+      <c r="K20" s="1">
+        <v>13.26</v>
+      </c>
+      <c r="L20" s="1">
+        <v>17.55</v>
+      </c>
+      <c r="M20" s="1">
+        <v>-14.01</v>
+      </c>
+      <c r="N20" s="1">
+        <v>-14.01</v>
+      </c>
+      <c r="P20" s="4" cm="1">
+        <f t="array" ref="P20">AVERAGEA(ABS(G20:N20))</f>
+        <v>14.801250000000001</v>
+      </c>
+      <c r="R20" s="3">
+        <f>P20-ABS(P9)</f>
+        <v>-400.0100000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D21" s="2"/>
+      <c r="E21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="1">
+        <v>-0.85299999999999998</v>
+      </c>
+      <c r="G21" s="1">
+        <v>-34.44</v>
+      </c>
+      <c r="H21" s="1">
+        <v>-59.77</v>
+      </c>
+      <c r="I21" s="1">
+        <v>-59.77</v>
+      </c>
+      <c r="J21" s="1">
+        <v>42.96</v>
+      </c>
+      <c r="K21" s="1">
+        <v>35.549999999999997</v>
+      </c>
+      <c r="L21" s="1">
+        <v>35.549999999999997</v>
+      </c>
+      <c r="M21" s="1">
+        <v>22.08</v>
+      </c>
+      <c r="N21" s="1">
+        <v>-35.68</v>
+      </c>
+      <c r="P21" s="4" cm="1">
+        <f t="array" ref="P21">AVERAGEA(ABS(G21:N21))</f>
+        <v>40.725000000000001</v>
+      </c>
+      <c r="R21" s="3">
+        <f>P21-ABS(P10)</f>
+        <v>13.380000000000003</v>
+      </c>
+    </row>
+    <row r="22" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D22" s="2"/>
+      <c r="E22" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="1">
+        <v>-8.82</v>
+      </c>
+      <c r="G22" s="1">
+        <v>305.61</v>
+      </c>
+      <c r="H22" s="1">
+        <v>305.61</v>
+      </c>
+      <c r="I22" s="1">
+        <v>305.61</v>
+      </c>
+      <c r="J22" s="1">
+        <v>394.09</v>
+      </c>
+      <c r="K22" s="1">
+        <v>1834.73</v>
+      </c>
+      <c r="L22" s="1">
+        <v>394.09</v>
+      </c>
+      <c r="M22" s="1">
+        <v>305.61</v>
+      </c>
+      <c r="N22" s="1">
+        <v>245.4</v>
+      </c>
+      <c r="P22" s="4" cm="1">
+        <f t="array" ref="P22">AVERAGEA(ABS(G22:N22))</f>
+        <v>511.34375000000006</v>
+      </c>
+      <c r="R22" s="3">
+        <f>P22-ABS(P11)</f>
+        <v>-5749.4387500000003</v>
+      </c>
+    </row>
+    <row r="23" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D23" s="2"/>
+      <c r="E23" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="1">
+        <v>-3.51</v>
+      </c>
+      <c r="G23" s="1">
+        <v>-63.01</v>
+      </c>
+      <c r="H23" s="1">
+        <v>-63.01</v>
+      </c>
+      <c r="I23" s="1">
+        <v>-63.01</v>
+      </c>
+      <c r="J23" s="1">
+        <v>-26.66</v>
+      </c>
+      <c r="K23" s="1">
+        <v>-8.0399999999999991</v>
+      </c>
+      <c r="L23" s="1">
+        <v>-26.66</v>
+      </c>
+      <c r="M23" s="1">
+        <v>-63.01</v>
+      </c>
+      <c r="N23" s="1">
+        <v>-81.45</v>
+      </c>
+      <c r="P23" s="4" cm="1">
+        <f t="array" ref="P23">AVERAGEA(ABS(G23:N23))</f>
+        <v>49.356249999999996</v>
+      </c>
+      <c r="R23" s="3">
+        <f>P23-ABS(P12)</f>
+        <v>-280.09125</v>
+      </c>
+    </row>
+    <row r="24" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D24" s="2"/>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>-40.93</v>
+      </c>
+      <c r="H24" s="1">
+        <v>-40.93</v>
+      </c>
+      <c r="I24" s="1">
+        <v>-40.93</v>
+      </c>
+      <c r="J24" s="1">
+        <v>-42.12</v>
+      </c>
+      <c r="K24" s="1">
+        <v>74.12</v>
+      </c>
+      <c r="L24" s="1">
+        <v>-42.12</v>
+      </c>
+      <c r="M24" s="1">
+        <v>-40.93</v>
+      </c>
+      <c r="N24" s="1">
+        <v>-49.69</v>
+      </c>
+      <c r="P24" s="4" cm="1">
+        <f t="array" ref="P24">AVERAGEA(ABS(G24:N24))</f>
+        <v>46.471249999999998</v>
+      </c>
+      <c r="R24" s="3">
+        <f>P24-ABS(P13)</f>
+        <v>-594.17875000000004</v>
+      </c>
+    </row>
+    <row r="25" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="E25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" s="1">
+        <v>-29.1</v>
+      </c>
+      <c r="G25" s="1">
+        <v>-74.010000000000005</v>
+      </c>
+      <c r="H25" s="1">
+        <v>-74.010000000000005</v>
+      </c>
+      <c r="I25" s="1">
+        <v>-74.010000000000005</v>
+      </c>
+      <c r="J25" s="1">
+        <v>104.61</v>
+      </c>
+      <c r="K25" s="1">
+        <v>104.61</v>
+      </c>
+      <c r="L25" s="1">
+        <v>104.61</v>
+      </c>
+      <c r="M25" s="1">
+        <v>-74.010000000000005</v>
+      </c>
+      <c r="N25" s="1">
+        <v>-86.97</v>
+      </c>
+      <c r="P25" s="4" cm="1">
+        <f t="array" ref="P25">AVERAGEA(ABS(G25:N25))</f>
+        <v>87.105000000000004</v>
+      </c>
+      <c r="R25" s="3">
+        <f>P25-ABS(P14)</f>
+        <v>-430.23874999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D27" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D28" s="5"/>
+      <c r="E28" t="s">
+        <v>0</v>
+      </c>
+      <c r="F28" s="1">
+        <v>-0.61399999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D29" s="5"/>
+      <c r="E29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="1">
+        <v>-0.42499999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D30" s="5"/>
+      <c r="E30" t="s">
+        <v>2</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="31" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D31" s="5"/>
+      <c r="E31" t="s">
+        <v>3</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D32" s="5"/>
+      <c r="E32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0.40200000000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D33" s="5"/>
+      <c r="E33" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="1">
+        <v>-0.85299999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D34" s="5"/>
+      <c r="E34" t="s">
+        <v>5</v>
+      </c>
+      <c r="F34" s="1">
+        <v>-8.82</v>
+      </c>
+    </row>
+    <row r="35" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D35" s="5"/>
+      <c r="E35" t="s">
+        <v>6</v>
+      </c>
+      <c r="F35" s="1">
+        <v>-3.51</v>
+      </c>
+    </row>
+    <row r="36" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D36" s="5"/>
+      <c r="E36" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="E37" t="s">
+        <v>7</v>
+      </c>
+      <c r="F37" s="1">
+        <v>-29.1</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F5:G14">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G14">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5:N14">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
+  <mergeCells count="3">
+    <mergeCell ref="D5:D14"/>
+    <mergeCell ref="D15:D24"/>
+    <mergeCell ref="D27:D36"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Errors.xlsx
+++ b/Errors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3975CB-BE00-4CFD-A1BD-9944EF6B09EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D382B8B4-4263-4731-8D41-53FE962DE1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{30A902C1-FA37-4575-AF65-6E09AA660DA0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30A902C1-FA37-4575-AF65-6E09AA660DA0}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="25">
   <si>
     <t>mt</t>
   </si>
@@ -130,6 +130,9 @@
   </si>
   <si>
     <t>New with normalised DB</t>
+  </si>
+  <si>
+    <t>MPR</t>
   </si>
 </sst>
 </file>
@@ -177,12 +180,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -521,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{556AB3AE-072F-44CD-A5AF-40E7BF9562B8}">
-  <dimension ref="D4:R37"/>
+  <dimension ref="D4:S37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="6" max="6" width="15.5546875" customWidth="1"/>
@@ -535,7 +538,7 @@
     <col min="14" max="14" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="4:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="4:19" x14ac:dyDescent="0.3">
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
         <v>8</v>
@@ -564,12 +567,15 @@
       <c r="N4" t="s">
         <v>18</v>
       </c>
-      <c r="P4" t="s">
+      <c r="O4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="4:18" x14ac:dyDescent="0.3">
-      <c r="D5" s="2" t="s">
+    <row r="5" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="D5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E5" t="s">
@@ -600,13 +606,13 @@
       <c r="N5" s="1">
         <v>-3.27</v>
       </c>
-      <c r="P5" s="4" cm="1">
-        <f t="array" ref="P5">AVERAGEA(ABS(G5:N5))</f>
+      <c r="Q5" s="3" cm="1">
+        <f t="array" ref="Q5">AVERAGEA(ABS(G5:N5))</f>
         <v>3.8187500000000001</v>
       </c>
     </row>
-    <row r="6" spans="4:18" x14ac:dyDescent="0.3">
-      <c r="D6" s="2"/>
+    <row r="6" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="D6" s="4"/>
       <c r="E6" t="s">
         <v>1</v>
       </c>
@@ -635,13 +641,13 @@
       <c r="N6" s="1">
         <v>-28.73</v>
       </c>
-      <c r="P6" s="4" cm="1">
-        <f t="array" ref="P6">AVERAGEA(ABS(G6:N6))</f>
+      <c r="Q6" s="3" cm="1">
+        <f t="array" ref="Q6">AVERAGEA(ABS(G6:N6))</f>
         <v>10.442499999999999</v>
       </c>
     </row>
-    <row r="7" spans="4:18" x14ac:dyDescent="0.3">
-      <c r="D7" s="2"/>
+    <row r="7" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="D7" s="4"/>
       <c r="E7" t="s">
         <v>2</v>
       </c>
@@ -670,13 +676,13 @@
       <c r="N7" s="1">
         <v>1.62</v>
       </c>
-      <c r="P7" s="4" cm="1">
-        <f t="array" ref="P7">AVERAGEA(ABS(G7:N7))</f>
+      <c r="Q7" s="3" cm="1">
+        <f t="array" ref="Q7">AVERAGEA(ABS(G7:N7))</f>
         <v>7.0075000000000003</v>
       </c>
     </row>
-    <row r="8" spans="4:18" x14ac:dyDescent="0.3">
-      <c r="D8" s="2"/>
+    <row r="8" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="D8" s="4"/>
       <c r="E8" t="s">
         <v>3</v>
       </c>
@@ -707,13 +713,13 @@
       <c r="N8" s="1">
         <v>0</v>
       </c>
-      <c r="P8" s="4" cm="1">
-        <f t="array" ref="P8">AVERAGEA(ABS(G8:N8))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="4:18" x14ac:dyDescent="0.3">
-      <c r="D9" s="2"/>
+      <c r="Q8" s="3" cm="1">
+        <f t="array" ref="Q8">AVERAGEA(ABS(G8:N8))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="D9" s="4"/>
       <c r="E9" t="s">
         <v>9</v>
       </c>
@@ -744,13 +750,13 @@
       <c r="N9" s="1">
         <v>-14.01</v>
       </c>
-      <c r="P9" s="4" cm="1">
-        <f t="array" ref="P9">AVERAGEA(ABS(G9:N9))</f>
+      <c r="Q9" s="3" cm="1">
+        <f t="array" ref="Q9">AVERAGEA(ABS(G9:N9))</f>
         <v>414.81125000000009</v>
       </c>
     </row>
-    <row r="10" spans="4:18" x14ac:dyDescent="0.3">
-      <c r="D10" s="2"/>
+    <row r="10" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="D10" s="4"/>
       <c r="E10" t="s">
         <v>4</v>
       </c>
@@ -779,13 +785,13 @@
       <c r="N10" s="1">
         <v>-31.18</v>
       </c>
-      <c r="P10" s="4" cm="1">
-        <f t="array" ref="P10">AVERAGEA(ABS(G10:N10))</f>
+      <c r="Q10" s="3" cm="1">
+        <f t="array" ref="Q10">AVERAGEA(ABS(G10:N10))</f>
         <v>27.344999999999999</v>
       </c>
     </row>
-    <row r="11" spans="4:18" x14ac:dyDescent="0.3">
-      <c r="D11" s="2"/>
+    <row r="11" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="D11" s="4"/>
       <c r="E11" t="s">
         <v>5</v>
       </c>
@@ -816,13 +822,13 @@
       <c r="N11" s="1">
         <v>355.27</v>
       </c>
-      <c r="P11" s="4" cm="1">
-        <f t="array" ref="P11">AVERAGEA(ABS(G11:N11))</f>
+      <c r="Q11" s="3" cm="1">
+        <f t="array" ref="Q11">AVERAGEA(ABS(G11:N11))</f>
         <v>6260.7825000000003</v>
       </c>
     </row>
-    <row r="12" spans="4:18" x14ac:dyDescent="0.3">
-      <c r="D12" s="2"/>
+    <row r="12" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="D12" s="4"/>
       <c r="E12" t="s">
         <v>6</v>
       </c>
@@ -853,13 +859,13 @@
       <c r="N12" s="1">
         <v>-6.64</v>
       </c>
-      <c r="P12" s="4" cm="1">
-        <f t="array" ref="P12">AVERAGEA(ABS(G12:N12))</f>
+      <c r="Q12" s="3" cm="1">
+        <f t="array" ref="Q12">AVERAGEA(ABS(G12:N12))</f>
         <v>329.44749999999999</v>
       </c>
     </row>
-    <row r="13" spans="4:18" x14ac:dyDescent="0.3">
-      <c r="D13" s="2"/>
+    <row r="13" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="D13" s="4"/>
       <c r="E13" t="s">
         <v>10</v>
       </c>
@@ -890,13 +896,13 @@
       <c r="N13" s="1">
         <v>-22.26</v>
       </c>
-      <c r="P13" s="4" cm="1">
-        <f t="array" ref="P13">AVERAGEA(ABS(G13:N13))</f>
+      <c r="Q13" s="3" cm="1">
+        <f t="array" ref="Q13">AVERAGEA(ABS(G13:N13))</f>
         <v>640.65</v>
       </c>
     </row>
-    <row r="14" spans="4:18" x14ac:dyDescent="0.3">
-      <c r="D14" s="2"/>
+    <row r="14" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="D14" s="4"/>
       <c r="E14" t="s">
         <v>7</v>
       </c>
@@ -927,13 +933,13 @@
       <c r="N14" s="1">
         <v>-38.71</v>
       </c>
-      <c r="P14" s="4" cm="1">
-        <f t="array" ref="P14">AVERAGEA(ABS(G14:N14))</f>
+      <c r="Q14" s="3" cm="1">
+        <f t="array" ref="Q14">AVERAGEA(ABS(G14:N14))</f>
         <v>517.34375</v>
       </c>
     </row>
-    <row r="15" spans="4:18" x14ac:dyDescent="0.3">
-      <c r="D15" s="2" t="s">
+    <row r="15" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="D15" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E15" s="1"/>
@@ -964,12 +970,12 @@
       <c r="N15" t="s">
         <v>18</v>
       </c>
-      <c r="R15" t="s">
+      <c r="S15" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="4:18" x14ac:dyDescent="0.3">
-      <c r="D16" s="2"/>
+    <row r="16" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="D16" s="4"/>
       <c r="E16" t="s">
         <v>0</v>
       </c>
@@ -1000,17 +1006,20 @@
       <c r="N16" s="1">
         <v>-11.17</v>
       </c>
-      <c r="P16" s="4" cm="1">
-        <f t="array" ref="P16">AVERAGEA(ABS(G16:N16))</f>
+      <c r="O16">
+        <v>5.25</v>
+      </c>
+      <c r="Q16" s="3" cm="1">
+        <f t="array" ref="Q16">AVERAGEA(ABS(G16:N16))</f>
         <v>8.4625000000000004</v>
       </c>
-      <c r="R16" s="3">
-        <f>P16-ABS(P5)</f>
+      <c r="S16" s="2">
+        <f t="shared" ref="S16:S25" si="0">Q16-ABS(Q5)</f>
         <v>4.6437500000000007</v>
       </c>
     </row>
-    <row r="17" spans="4:18" x14ac:dyDescent="0.3">
-      <c r="D17" s="2"/>
+    <row r="17" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="D17" s="4"/>
       <c r="E17" t="s">
         <v>1</v>
       </c>
@@ -1041,17 +1050,20 @@
       <c r="N17" s="1">
         <v>-52.77</v>
       </c>
-      <c r="P17" s="4" cm="1">
-        <f t="array" ref="P17">AVERAGEA(ABS(G17:N17))</f>
+      <c r="O17">
+        <v>-2.78</v>
+      </c>
+      <c r="Q17" s="3" cm="1">
+        <f t="array" ref="Q17">AVERAGEA(ABS(G17:N17))</f>
         <v>23.756250000000001</v>
       </c>
-      <c r="R17" s="3">
-        <f>P17-ABS(P6)</f>
+      <c r="S17" s="2">
+        <f t="shared" si="0"/>
         <v>13.313750000000002</v>
       </c>
     </row>
-    <row r="18" spans="4:18" x14ac:dyDescent="0.3">
-      <c r="D18" s="2"/>
+    <row r="18" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="D18" s="4"/>
       <c r="E18" t="s">
         <v>2</v>
       </c>
@@ -1082,17 +1094,20 @@
       <c r="N18" s="1">
         <v>-6.68</v>
       </c>
-      <c r="P18" s="4" cm="1">
-        <f t="array" ref="P18">AVERAGEA(ABS(G18:N18))</f>
+      <c r="O18">
+        <v>10.58</v>
+      </c>
+      <c r="Q18" s="3" cm="1">
+        <f t="array" ref="Q18">AVERAGEA(ABS(G18:N18))</f>
         <v>10.153749999999999</v>
       </c>
-      <c r="R18" s="3">
-        <f>P18-ABS(P7)</f>
+      <c r="S18" s="2">
+        <f t="shared" si="0"/>
         <v>3.1462499999999984</v>
       </c>
     </row>
-    <row r="19" spans="4:18" x14ac:dyDescent="0.3">
-      <c r="D19" s="2"/>
+    <row r="19" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="D19" s="4"/>
       <c r="E19" t="s">
         <v>3</v>
       </c>
@@ -1123,17 +1138,20 @@
       <c r="N19" s="1">
         <v>0</v>
       </c>
-      <c r="P19" s="4" cm="1">
-        <f t="array" ref="P19">AVERAGEA(ABS(G19:N19))</f>
-        <v>0</v>
-      </c>
-      <c r="R19" s="3">
-        <f>P19-ABS(P8)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="4:18" x14ac:dyDescent="0.3">
-      <c r="D20" s="2"/>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="3" cm="1">
+        <f t="array" ref="Q19">AVERAGEA(ABS(G19:N19))</f>
+        <v>0</v>
+      </c>
+      <c r="S19" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="D20" s="4"/>
       <c r="E20" t="s">
         <v>9</v>
       </c>
@@ -1164,17 +1182,20 @@
       <c r="N20" s="1">
         <v>-14.01</v>
       </c>
-      <c r="P20" s="4" cm="1">
-        <f t="array" ref="P20">AVERAGEA(ABS(G20:N20))</f>
+      <c r="O20">
+        <v>22.3</v>
+      </c>
+      <c r="Q20" s="3" cm="1">
+        <f t="array" ref="Q20">AVERAGEA(ABS(G20:N20))</f>
         <v>14.801250000000001</v>
       </c>
-      <c r="R20" s="3">
-        <f>P20-ABS(P9)</f>
+      <c r="S20" s="2">
+        <f t="shared" si="0"/>
         <v>-400.0100000000001</v>
       </c>
     </row>
-    <row r="21" spans="4:18" x14ac:dyDescent="0.3">
-      <c r="D21" s="2"/>
+    <row r="21" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="D21" s="4"/>
       <c r="E21" t="s">
         <v>4</v>
       </c>
@@ -1205,17 +1226,20 @@
       <c r="N21" s="1">
         <v>-35.68</v>
       </c>
-      <c r="P21" s="4" cm="1">
-        <f t="array" ref="P21">AVERAGEA(ABS(G21:N21))</f>
+      <c r="O21">
+        <v>15.39</v>
+      </c>
+      <c r="Q21" s="3" cm="1">
+        <f t="array" ref="Q21">AVERAGEA(ABS(G21:N21))</f>
         <v>40.725000000000001</v>
       </c>
-      <c r="R21" s="3">
-        <f>P21-ABS(P10)</f>
+      <c r="S21" s="2">
+        <f t="shared" si="0"/>
         <v>13.380000000000003</v>
       </c>
     </row>
-    <row r="22" spans="4:18" x14ac:dyDescent="0.3">
-      <c r="D22" s="2"/>
+    <row r="22" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="D22" s="4"/>
       <c r="E22" t="s">
         <v>5</v>
       </c>
@@ -1246,17 +1270,20 @@
       <c r="N22" s="1">
         <v>245.4</v>
       </c>
-      <c r="P22" s="4" cm="1">
-        <f t="array" ref="P22">AVERAGEA(ABS(G22:N22))</f>
+      <c r="O22">
+        <v>391.46</v>
+      </c>
+      <c r="Q22" s="3" cm="1">
+        <f t="array" ref="Q22">AVERAGEA(ABS(G22:N22))</f>
         <v>511.34375000000006</v>
       </c>
-      <c r="R22" s="3">
-        <f>P22-ABS(P11)</f>
+      <c r="S22" s="2">
+        <f t="shared" si="0"/>
         <v>-5749.4387500000003</v>
       </c>
     </row>
-    <row r="23" spans="4:18" x14ac:dyDescent="0.3">
-      <c r="D23" s="2"/>
+    <row r="23" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="D23" s="4"/>
       <c r="E23" t="s">
         <v>6</v>
       </c>
@@ -1287,17 +1314,20 @@
       <c r="N23" s="1">
         <v>-81.45</v>
       </c>
-      <c r="P23" s="4" cm="1">
-        <f t="array" ref="P23">AVERAGEA(ABS(G23:N23))</f>
+      <c r="O23">
+        <v>-33.93</v>
+      </c>
+      <c r="Q23" s="3" cm="1">
+        <f t="array" ref="Q23">AVERAGEA(ABS(G23:N23))</f>
         <v>49.356249999999996</v>
       </c>
-      <c r="R23" s="3">
-        <f>P23-ABS(P12)</f>
+      <c r="S23" s="2">
+        <f t="shared" si="0"/>
         <v>-280.09125</v>
       </c>
     </row>
-    <row r="24" spans="4:18" x14ac:dyDescent="0.3">
-      <c r="D24" s="2"/>
+    <row r="24" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="D24" s="4"/>
       <c r="E24" t="s">
         <v>10</v>
       </c>
@@ -1328,16 +1358,19 @@
       <c r="N24" s="1">
         <v>-49.69</v>
       </c>
-      <c r="P24" s="4" cm="1">
-        <f t="array" ref="P24">AVERAGEA(ABS(G24:N24))</f>
+      <c r="O24">
+        <v>-41.78</v>
+      </c>
+      <c r="Q24" s="3" cm="1">
+        <f t="array" ref="Q24">AVERAGEA(ABS(G24:N24))</f>
         <v>46.471249999999998</v>
       </c>
-      <c r="R24" s="3">
-        <f>P24-ABS(P13)</f>
+      <c r="S24" s="2">
+        <f t="shared" si="0"/>
         <v>-594.17875000000004</v>
       </c>
     </row>
-    <row r="25" spans="4:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="4:19" x14ac:dyDescent="0.3">
       <c r="E25" t="s">
         <v>7</v>
       </c>
@@ -1368,16 +1401,19 @@
       <c r="N25" s="1">
         <v>-86.97</v>
       </c>
-      <c r="P25" s="4" cm="1">
-        <f t="array" ref="P25">AVERAGEA(ABS(G25:N25))</f>
+      <c r="O25">
+        <v>102.79</v>
+      </c>
+      <c r="Q25" s="3" cm="1">
+        <f t="array" ref="Q25">AVERAGEA(ABS(G25:N25))</f>
         <v>87.105000000000004</v>
       </c>
-      <c r="R25" s="3">
-        <f>P25-ABS(P14)</f>
+      <c r="S25" s="2">
+        <f t="shared" si="0"/>
         <v>-430.23874999999998</v>
       </c>
     </row>
-    <row r="27" spans="4:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="4:19" x14ac:dyDescent="0.3">
       <c r="D27" s="5" t="s">
         <v>23</v>
       </c>
@@ -1386,7 +1422,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="4:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="4:19" x14ac:dyDescent="0.3">
       <c r="D28" s="5"/>
       <c r="E28" t="s">
         <v>0</v>
@@ -1395,7 +1431,7 @@
         <v>-0.61399999999999999</v>
       </c>
     </row>
-    <row r="29" spans="4:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="4:19" x14ac:dyDescent="0.3">
       <c r="D29" s="5"/>
       <c r="E29" t="s">
         <v>1</v>
@@ -1404,7 +1440,7 @@
         <v>-0.42499999999999999</v>
       </c>
     </row>
-    <row r="30" spans="4:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="4:19" x14ac:dyDescent="0.3">
       <c r="D30" s="5"/>
       <c r="E30" t="s">
         <v>2</v>
@@ -1413,7 +1449,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="31" spans="4:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="4:19" x14ac:dyDescent="0.3">
       <c r="D31" s="5"/>
       <c r="E31" t="s">
         <v>3</v>
@@ -1422,7 +1458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="4:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="4:19" x14ac:dyDescent="0.3">
       <c r="D32" s="5"/>
       <c r="E32" t="s">
         <v>9</v>

--- a/Errors.xlsx
+++ b/Errors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D382B8B4-4263-4731-8D41-53FE962DE1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01081D58-844E-4F28-A687-9AFA87F047AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30A902C1-FA37-4575-AF65-6E09AA660DA0}"/>
+    <workbookView xWindow="-44544" yWindow="744" windowWidth="21600" windowHeight="11592" xr2:uid="{30A902C1-FA37-4575-AF65-6E09AA660DA0}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -525,20 +525,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{556AB3AE-072F-44CD-A5AF-40E7BF9562B8}">
   <dimension ref="D4:S37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="15.5546875" customWidth="1"/>
-    <col min="7" max="7" width="24.6640625" customWidth="1"/>
-    <col min="8" max="8" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.109375" customWidth="1"/>
-    <col min="11" max="11" width="22.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="24.7109375" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.140625" customWidth="1"/>
+    <col min="11" max="11" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="4:19" x14ac:dyDescent="0.25">
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
         <v>8</v>
@@ -574,7 +574,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D5" s="4" t="s">
         <v>19</v>
       </c>
@@ -611,7 +611,7 @@
         <v>3.8187500000000001</v>
       </c>
     </row>
-    <row r="6" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D6" s="4"/>
       <c r="E6" t="s">
         <v>1</v>
@@ -646,7 +646,7 @@
         <v>10.442499999999999</v>
       </c>
     </row>
-    <row r="7" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D7" s="4"/>
       <c r="E7" t="s">
         <v>2</v>
@@ -681,7 +681,7 @@
         <v>7.0075000000000003</v>
       </c>
     </row>
-    <row r="8" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D8" s="4"/>
       <c r="E8" t="s">
         <v>3</v>
@@ -718,7 +718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D9" s="4"/>
       <c r="E9" t="s">
         <v>9</v>
@@ -755,7 +755,7 @@
         <v>414.81125000000009</v>
       </c>
     </row>
-    <row r="10" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D10" s="4"/>
       <c r="E10" t="s">
         <v>4</v>
@@ -790,7 +790,7 @@
         <v>27.344999999999999</v>
       </c>
     </row>
-    <row r="11" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D11" s="4"/>
       <c r="E11" t="s">
         <v>5</v>
@@ -827,7 +827,7 @@
         <v>6260.7825000000003</v>
       </c>
     </row>
-    <row r="12" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D12" s="4"/>
       <c r="E12" t="s">
         <v>6</v>
@@ -864,7 +864,7 @@
         <v>329.44749999999999</v>
       </c>
     </row>
-    <row r="13" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D13" s="4"/>
       <c r="E13" t="s">
         <v>10</v>
@@ -901,7 +901,7 @@
         <v>640.65</v>
       </c>
     </row>
-    <row r="14" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D14" s="4"/>
       <c r="E14" t="s">
         <v>7</v>
@@ -938,7 +938,7 @@
         <v>517.34375</v>
       </c>
     </row>
-    <row r="15" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D15" s="4" t="s">
         <v>20</v>
       </c>
@@ -974,7 +974,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D16" s="4"/>
       <c r="E16" t="s">
         <v>0</v>
@@ -1018,7 +1018,7 @@
         <v>4.6437500000000007</v>
       </c>
     </row>
-    <row r="17" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D17" s="4"/>
       <c r="E17" t="s">
         <v>1</v>
@@ -1062,7 +1062,7 @@
         <v>13.313750000000002</v>
       </c>
     </row>
-    <row r="18" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D18" s="4"/>
       <c r="E18" t="s">
         <v>2</v>
@@ -1106,7 +1106,7 @@
         <v>3.1462499999999984</v>
       </c>
     </row>
-    <row r="19" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D19" s="4"/>
       <c r="E19" t="s">
         <v>3</v>
@@ -1150,7 +1150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D20" s="4"/>
       <c r="E20" t="s">
         <v>9</v>
@@ -1194,7 +1194,7 @@
         <v>-400.0100000000001</v>
       </c>
     </row>
-    <row r="21" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D21" s="4"/>
       <c r="E21" t="s">
         <v>4</v>
@@ -1238,7 +1238,7 @@
         <v>13.380000000000003</v>
       </c>
     </row>
-    <row r="22" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D22" s="4"/>
       <c r="E22" t="s">
         <v>5</v>
@@ -1282,7 +1282,7 @@
         <v>-5749.4387500000003</v>
       </c>
     </row>
-    <row r="23" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D23" s="4"/>
       <c r="E23" t="s">
         <v>6</v>
@@ -1326,7 +1326,7 @@
         <v>-280.09125</v>
       </c>
     </row>
-    <row r="24" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D24" s="4"/>
       <c r="E24" t="s">
         <v>10</v>
@@ -1370,7 +1370,7 @@
         <v>-594.17875000000004</v>
       </c>
     </row>
-    <row r="25" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="4:19" x14ac:dyDescent="0.25">
       <c r="E25" t="s">
         <v>7</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>-430.23874999999998</v>
       </c>
     </row>
-    <row r="27" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D27" s="5" t="s">
         <v>23</v>
       </c>
@@ -1422,7 +1422,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D28" s="5"/>
       <c r="E28" t="s">
         <v>0</v>
@@ -1431,7 +1431,7 @@
         <v>-0.61399999999999999</v>
       </c>
     </row>
-    <row r="29" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D29" s="5"/>
       <c r="E29" t="s">
         <v>1</v>
@@ -1440,7 +1440,7 @@
         <v>-0.42499999999999999</v>
       </c>
     </row>
-    <row r="30" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D30" s="5"/>
       <c r="E30" t="s">
         <v>2</v>
@@ -1449,7 +1449,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="31" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D31" s="5"/>
       <c r="E31" t="s">
         <v>3</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="32" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D32" s="5"/>
       <c r="E32" t="s">
         <v>9</v>
@@ -1467,7 +1467,7 @@
         <v>0.40200000000000002</v>
       </c>
     </row>
-    <row r="33" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D33" s="5"/>
       <c r="E33" t="s">
         <v>4</v>
@@ -1476,7 +1476,7 @@
         <v>-0.85299999999999998</v>
       </c>
     </row>
-    <row r="34" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D34" s="5"/>
       <c r="E34" t="s">
         <v>5</v>
@@ -1485,7 +1485,7 @@
         <v>-8.82</v>
       </c>
     </row>
-    <row r="35" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D35" s="5"/>
       <c r="E35" t="s">
         <v>6</v>
@@ -1494,7 +1494,7 @@
         <v>-3.51</v>
       </c>
     </row>
-    <row r="36" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D36" s="5"/>
       <c r="E36" t="s">
         <v>10</v>
@@ -1503,7 +1503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E37" t="s">
         <v>7</v>
       </c>
